--- a/results/section4.xlsx
+++ b/results/section4.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="6940" tabRatio="532"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="6940" tabRatio="532" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -255,10 +255,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -585,12 +585,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
         <v>12</v>
@@ -717,12 +717,12 @@
       <c r="K11" s="5"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
@@ -922,12 +922,12 @@
       <c r="G25" s="8"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="8"/>
@@ -1116,12 +1116,12 @@
       <c r="G42" s="12"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A44" s="20" t="s">
+      <c r="A44" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="1"/>
       <c r="H44" s="3"/>
     </row>
@@ -1395,12 +1395,12 @@
       <c r="I58" s="12"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A59" s="20" t="s">
+      <c r="A59" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B59" s="20"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
       <c r="E59" s="10"/>
       <c r="F59" s="10"/>
       <c r="G59" s="10"/>
@@ -1540,12 +1540,12 @@
       <c r="G67" s="16"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="20" t="s">
+      <c r="A68" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
       <c r="E68" s="18"/>
       <c r="F68" s="18"/>
     </row>
@@ -1741,12 +1741,12 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A84" s="20" t="s">
+      <c r="A84" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B84" s="20"/>
-      <c r="C84" s="20"/>
-      <c r="D84" s="20"/>
+      <c r="B84" s="21"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="21"/>
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
     </row>
@@ -1970,9 +1970,7 @@
       <c r="F99" s="18"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="14">
-        <v>341152</v>
-      </c>
+      <c r="A100" s="14"/>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
       <c r="D100" s="18"/>
@@ -1980,9 +1978,7 @@
       <c r="F100" s="18"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="14">
-        <v>387587</v>
-      </c>
+      <c r="A101" s="14"/>
       <c r="B101" s="18"/>
       <c r="C101" s="18"/>
       <c r="D101" s="18"/>
@@ -1990,9 +1986,7 @@
       <c r="F101" s="18"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="14">
-        <v>227278</v>
-      </c>
+      <c r="A102" s="14"/>
       <c r="B102" s="18"/>
       <c r="C102" s="18"/>
       <c r="D102" s="18"/>
@@ -2000,10 +1994,7 @@
       <c r="F102" s="18"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="21">
-        <f>SUM(A100:A102)</f>
-        <v>956017</v>
-      </c>
+      <c r="A103" s="20"/>
       <c r="B103" s="18"/>
       <c r="C103" s="18"/>
       <c r="D103" s="18"/>
@@ -2077,12 +2068,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
       <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
